--- a/PV_ICE/baselines/SupportingMaterial/mass-input-glass-Marketshare_Thickness_G-GvG-B.xlsx
+++ b/PV_ICE/baselines/SupportingMaterial/mass-input-glass-Marketshare_Thickness_G-GvG-B.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hmirletz\Documents\GitHub\PV_ICE\PV_ICE\baselines\SupportingMaterial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5BD3AE74-ABC8-4F73-9C31-D220142FC5AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B566CC3A-33A8-44C9-85F5-5DE1679BB725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{85772F83-15B9-4D17-B171-BF64CB55D870}"/>
   </bookViews>
   <sheets>
     <sheet name="Marketshare_glass" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="50">
   <si>
     <t>Year</t>
   </si>
@@ -158,6 +171,18 @@
   </si>
   <si>
     <t>ITRPV 2024 reporting g-b and g-g seperately</t>
+  </si>
+  <si>
+    <t>ITRPV 2025, Fig. 61</t>
+  </si>
+  <si>
+    <t>ITRPV 2025, Fig. 48</t>
+  </si>
+  <si>
+    <t>ITRPV 2025, fig.47</t>
+  </si>
+  <si>
+    <t>ITRPV 2025, Fig. 51</t>
   </si>
 </sst>
 </file>
@@ -1700,174 +1725,213 @@
         <v>2024</v>
       </c>
       <c r="B32">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C32">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="J32">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="K32">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O32">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P32">
         <v>5</v>
       </c>
       <c r="Q32" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="R32">
         <v>1</v>
       </c>
       <c r="S32">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="T32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U32" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2025</v>
       </c>
+      <c r="B33">
+        <v>40</v>
+      </c>
+      <c r="C33">
+        <v>58</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33" t="s">
+        <v>46</v>
+      </c>
+      <c r="J33">
+        <v>90</v>
+      </c>
+      <c r="K33">
+        <v>10</v>
+      </c>
+      <c r="M33" t="s">
+        <v>47</v>
+      </c>
+      <c r="N33">
+        <v>8</v>
+      </c>
+      <c r="O33">
+        <v>87</v>
+      </c>
+      <c r="P33">
+        <v>5</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>48</v>
+      </c>
+      <c r="R33">
+        <v>1</v>
+      </c>
+      <c r="S33">
+        <v>92</v>
+      </c>
+      <c r="T33">
+        <v>7</v>
+      </c>
+      <c r="U33" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2026</v>
       </c>
-      <c r="B34">
-        <v>38</v>
-      </c>
-      <c r="C34">
-        <v>60</v>
-      </c>
-      <c r="D34">
-        <v>2</v>
-      </c>
-      <c r="E34" t="s">
-        <v>26</v>
-      </c>
-      <c r="J34">
-        <v>85</v>
-      </c>
-      <c r="K34">
-        <v>15</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34" t="s">
-        <v>43</v>
-      </c>
-      <c r="N34">
-        <v>4</v>
-      </c>
-      <c r="O34">
-        <v>88</v>
-      </c>
-      <c r="P34">
-        <v>8</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>35</v>
-      </c>
-      <c r="R34">
-        <v>1</v>
-      </c>
-      <c r="S34">
-        <v>89</v>
-      </c>
-      <c r="T34">
-        <v>10</v>
-      </c>
-      <c r="U34" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2027</v>
       </c>
+      <c r="B35">
+        <v>30</v>
+      </c>
+      <c r="C35">
+        <v>67</v>
+      </c>
+      <c r="D35">
+        <v>3</v>
+      </c>
+      <c r="E35" t="s">
+        <v>46</v>
+      </c>
+      <c r="J35">
+        <v>88</v>
+      </c>
+      <c r="K35">
+        <v>12</v>
+      </c>
+      <c r="M35" t="s">
+        <v>47</v>
+      </c>
+      <c r="N35">
+        <v>10</v>
+      </c>
+      <c r="O35">
+        <v>86</v>
+      </c>
+      <c r="P35">
+        <v>4</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>48</v>
+      </c>
+      <c r="R35">
+        <v>1</v>
+      </c>
+      <c r="S35">
+        <v>89</v>
+      </c>
+      <c r="T35">
+        <v>10</v>
+      </c>
+      <c r="U35" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2028</v>
       </c>
-      <c r="B36">
-        <v>30</v>
-      </c>
-      <c r="C36">
-        <v>68</v>
-      </c>
-      <c r="D36">
-        <v>2</v>
-      </c>
-      <c r="E36" t="s">
-        <v>26</v>
-      </c>
-      <c r="J36">
-        <v>85</v>
-      </c>
-      <c r="K36">
-        <v>15</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36" t="s">
-        <v>43</v>
-      </c>
-      <c r="N36">
-        <v>3</v>
-      </c>
-      <c r="O36">
-        <v>87</v>
-      </c>
-      <c r="P36">
-        <v>10</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>35</v>
-      </c>
-      <c r="R36">
-        <v>1</v>
-      </c>
-      <c r="S36">
-        <v>84</v>
-      </c>
-      <c r="T36">
-        <v>15</v>
-      </c>
-      <c r="U36" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2029</v>
       </c>
+      <c r="B37">
+        <v>25</v>
+      </c>
+      <c r="C37">
+        <v>71</v>
+      </c>
+      <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="E37" t="s">
+        <v>46</v>
+      </c>
+      <c r="J37">
+        <v>85</v>
+      </c>
+      <c r="K37">
+        <v>15</v>
+      </c>
+      <c r="M37" t="s">
+        <v>47</v>
+      </c>
+      <c r="N37">
+        <v>12</v>
+      </c>
+      <c r="O37">
+        <v>84</v>
+      </c>
+      <c r="P37">
+        <v>4</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>48</v>
+      </c>
+      <c r="R37">
+        <v>1</v>
+      </c>
+      <c r="S37">
+        <v>85</v>
+      </c>
+      <c r="T37">
+        <v>14</v>
+      </c>
+      <c r="U37" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A38">
@@ -1878,59 +1942,56 @@
       <c r="A39">
         <v>2031</v>
       </c>
-      <c r="B39">
-        <v>25</v>
-      </c>
-      <c r="C39">
-        <v>72</v>
-      </c>
-      <c r="D39">
-        <v>3</v>
-      </c>
-      <c r="E39" t="s">
-        <v>26</v>
-      </c>
-      <c r="J39">
-        <v>80</v>
-      </c>
-      <c r="K39">
-        <v>19</v>
-      </c>
-      <c r="L39">
-        <v>1</v>
-      </c>
-      <c r="M39" t="s">
-        <v>43</v>
-      </c>
-      <c r="N39">
-        <v>3</v>
-      </c>
-      <c r="O39">
-        <v>82</v>
-      </c>
-      <c r="P39">
-        <v>15</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>35</v>
-      </c>
-      <c r="R39">
-        <v>1</v>
-      </c>
-      <c r="S39">
-        <v>79</v>
-      </c>
-      <c r="T39">
-        <v>20</v>
-      </c>
-      <c r="U39" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>2032</v>
       </c>
+      <c r="B40">
+        <v>20</v>
+      </c>
+      <c r="C40">
+        <v>75</v>
+      </c>
+      <c r="D40">
+        <v>5</v>
+      </c>
+      <c r="E40" t="s">
+        <v>46</v>
+      </c>
+      <c r="J40">
+        <v>82</v>
+      </c>
+      <c r="K40">
+        <v>18</v>
+      </c>
+      <c r="M40" t="s">
+        <v>47</v>
+      </c>
+      <c r="N40">
+        <v>14</v>
+      </c>
+      <c r="O40">
+        <v>83</v>
+      </c>
+      <c r="P40">
+        <v>3</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>48</v>
+      </c>
+      <c r="R40">
+        <v>1</v>
+      </c>
+      <c r="S40">
+        <v>81</v>
+      </c>
+      <c r="T40">
+        <v>18</v>
+      </c>
+      <c r="U40" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A41">
@@ -1941,58 +2002,55 @@
       <c r="A42">
         <v>2034</v>
       </c>
-      <c r="B42">
-        <v>23</v>
-      </c>
-      <c r="C42">
-        <v>73</v>
-      </c>
-      <c r="D42">
-        <v>4</v>
-      </c>
-      <c r="E42" t="s">
-        <v>26</v>
-      </c>
-      <c r="J42">
-        <v>77</v>
-      </c>
-      <c r="K42">
-        <v>22</v>
-      </c>
-      <c r="L42">
-        <v>1</v>
-      </c>
-      <c r="M42" t="s">
-        <v>43</v>
-      </c>
-      <c r="N42">
-        <v>2</v>
-      </c>
-      <c r="O42">
-        <v>78</v>
-      </c>
-      <c r="P42">
-        <v>20</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>35</v>
-      </c>
-      <c r="R42">
-        <v>1</v>
-      </c>
-      <c r="S42">
-        <v>74</v>
-      </c>
-      <c r="T42">
-        <v>25</v>
-      </c>
-      <c r="U42" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2035</v>
+      </c>
+      <c r="B43">
+        <v>20</v>
+      </c>
+      <c r="C43">
+        <v>75</v>
+      </c>
+      <c r="D43">
+        <v>5</v>
+      </c>
+      <c r="E43" t="s">
+        <v>46</v>
+      </c>
+      <c r="J43">
+        <v>80</v>
+      </c>
+      <c r="K43">
+        <v>20</v>
+      </c>
+      <c r="M43" t="s">
+        <v>47</v>
+      </c>
+      <c r="N43">
+        <v>14</v>
+      </c>
+      <c r="O43">
+        <v>83</v>
+      </c>
+      <c r="P43">
+        <v>3</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>48</v>
+      </c>
+      <c r="R43">
+        <v>1</v>
+      </c>
+      <c r="S43">
+        <v>79</v>
+      </c>
+      <c r="T43">
+        <v>20</v>
+      </c>
+      <c r="U43" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.35">
